--- a/data/trans_orig/P0802-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2007</t>
+          <t>Población según limitación a subir varios pisos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>580141</t>
+          <t>580220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>613671</t>
+          <t>615895</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>507759</t>
+          <t>505174</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>549994</t>
+          <t>548264</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1095880</t>
+          <t>1098434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1153662</t>
+          <t>1153579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56887</t>
+          <t>55372</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87076</t>
+          <t>87331</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106999</t>
+          <t>108027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147300</t>
+          <t>147526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172497</t>
+          <t>172478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222759</t>
+          <t>223767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36682</t>
+          <t>35878</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45813</t>
+          <t>47238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>45329</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74837</t>
+          <t>75138</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>814670</t>
+          <t>814412</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>857392</t>
+          <t>856524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>719512</t>
+          <t>717549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>774056</t>
+          <t>773070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1546759</t>
+          <t>1552477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1615451</t>
+          <t>1617000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74231</t>
+          <t>74536</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111193</t>
+          <t>111496</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>149949</t>
+          <t>147427</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>199892</t>
+          <t>198080</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>235243</t>
+          <t>231591</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>294563</t>
+          <t>291795</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23529</t>
+          <t>23367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47080</t>
+          <t>45895</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34914</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62555</t>
+          <t>62787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63911</t>
+          <t>63136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101315</t>
+          <t>99918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>553274</t>
+          <t>553704</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>590972</t>
+          <t>591978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>491204</t>
+          <t>489725</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>533840</t>
+          <t>533488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1057260</t>
+          <t>1060376</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1116698</t>
+          <t>1117025</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62885</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96451</t>
+          <t>96643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93845</t>
+          <t>92805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131356</t>
+          <t>129736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163598</t>
+          <t>165267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217823</t>
+          <t>215078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45042</t>
+          <t>45706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76208</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68696</t>
+          <t>68673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103821</t>
+          <t>102738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>790674</t>
+          <t>789168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>830799</t>
+          <t>829758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>771932</t>
+          <t>774289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>826527</t>
+          <t>831200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1581228</t>
+          <t>1579019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1648760</t>
+          <t>1644572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77320</t>
+          <t>78776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112635</t>
+          <t>112970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139714</t>
+          <t>138210</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187199</t>
+          <t>187453</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229181</t>
+          <t>230097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285415</t>
+          <t>288804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49254</t>
+          <t>50548</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>56032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91221</t>
+          <t>90795</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>90530</t>
+          <t>91566</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129635</t>
+          <t>133728</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2781204</t>
+          <t>2780770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2855843</t>
+          <t>2860304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2540493</t>
+          <t>2542685</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2643450</t>
+          <t>2641918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5345698</t>
+          <t>5353005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5477417</t>
+          <t>5475675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>301996</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>372599</t>
+          <t>371394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>528502</t>
+          <t>532418</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>619138</t>
+          <t>623494</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>851342</t>
+          <t>852849</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>963313</t>
+          <t>960674</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102165</t>
+          <t>101039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144279</t>
+          <t>143626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186830</t>
+          <t>184782</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>243588</t>
+          <t>243533</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>298915</t>
+          <t>301104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>372125</t>
+          <t>371522</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2012</t>
+          <t>Población según limitación a subir varios pisos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>569940</t>
+          <t>568256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>606390</t>
+          <t>608442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>484816</t>
+          <t>485124</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>532434</t>
+          <t>532619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1066463</t>
+          <t>1068120</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1129740</t>
+          <t>1129553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62729</t>
+          <t>62123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94541</t>
+          <t>97389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94921</t>
+          <t>92068</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136206</t>
+          <t>133333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167355</t>
+          <t>168197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219751</t>
+          <t>219574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49541</t>
+          <t>50831</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58102</t>
+          <t>57943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91648</t>
+          <t>90340</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90232</t>
+          <t>91308</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131978</t>
+          <t>131309</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>823035</t>
+          <t>826051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>872404</t>
+          <t>875306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,82 +3716,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>769676</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>739334</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>797659</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>74,65%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>71,7%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>77,36%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1620325</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1581751</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1656677</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>79,08%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>77,19%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>80,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>769676</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>740437</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>797974</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>74,65%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>71,81%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1620325</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1577806</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1653659</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>79,08%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>77,0%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94480</t>
+          <t>91483</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135767</t>
+          <t>133238</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130484</t>
+          <t>130220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178735</t>
+          <t>178453</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>233291</t>
+          <t>233512</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>296120</t>
+          <t>295602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39921</t>
+          <t>41388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70541</t>
+          <t>71612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89727</t>
+          <t>89957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131980</t>
+          <t>130751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138813</t>
+          <t>138983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188778</t>
+          <t>189934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>640445</t>
+          <t>641570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>680336</t>
+          <t>681602</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>572856</t>
+          <t>571810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>622207</t>
+          <t>621896</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1226955</t>
+          <t>1228361</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1292611</t>
+          <t>1290538</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47388</t>
+          <t>47658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78490</t>
+          <t>77833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87794</t>
+          <t>87009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128061</t>
+          <t>129158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142944</t>
+          <t>143334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195047</t>
+          <t>196334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48525</t>
+          <t>48406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57226</t>
+          <t>56831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90756</t>
+          <t>92039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83844</t>
+          <t>85322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127324</t>
+          <t>129024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>762286</t>
+          <t>763315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>811428</t>
+          <t>810327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>734059</t>
+          <t>735415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>792593</t>
+          <t>795001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1511188</t>
+          <t>1511620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1584704</t>
+          <t>1588644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88267</t>
+          <t>89190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130119</t>
+          <t>130635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171062</t>
+          <t>169285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>222335</t>
+          <t>222051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273424</t>
+          <t>271494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336517</t>
+          <t>335730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36441</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63926</t>
+          <t>66222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73296</t>
+          <t>76065</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111396</t>
+          <t>111042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118350</t>
+          <t>118773</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>165820</t>
+          <t>165388</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2843764</t>
+          <t>2847280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2930525</t>
+          <t>2935148</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2587845</t>
+          <t>2588235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2699763</t>
+          <t>2693905</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5468649</t>
+          <t>5464932</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5601630</t>
+          <t>5599342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>327119</t>
+          <t>321248</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>397194</t>
+          <t>396264</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>524396</t>
+          <t>529916</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>612693</t>
+          <t>615914</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>873280</t>
+          <t>873010</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>985866</t>
+          <t>986556</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148422</t>
+          <t>147007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>202521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>312034</t>
+          <t>313393</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>380918</t>
+          <t>385717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>474979</t>
+          <t>482134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>570104</t>
+          <t>568634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2016</t>
+          <t>Población según limitación a subir varios pisos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>548857</t>
+          <t>548967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>588302</t>
+          <t>586292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>479497</t>
+          <t>480763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>525383</t>
+          <t>524885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1042183</t>
+          <t>1042419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1101140</t>
+          <t>1101162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>58363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91889</t>
+          <t>89841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85514</t>
+          <t>84667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123824</t>
+          <t>124399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151941</t>
+          <t>152508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>202032</t>
+          <t>203328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44990</t>
+          <t>44614</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53375</t>
+          <t>52983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86689</t>
+          <t>85189</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81837</t>
+          <t>80143</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119028</t>
+          <t>119707</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>851892</t>
+          <t>854829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>897549</t>
+          <t>898118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>759218</t>
+          <t>757862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>818932</t>
+          <t>817804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1628941</t>
+          <t>1627291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1705100</t>
+          <t>1702006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86331</t>
+          <t>86223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127654</t>
+          <t>125783</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>136584</t>
+          <t>136527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186935</t>
+          <t>186916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>233846</t>
+          <t>236342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>294408</t>
+          <t>300096</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54941</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72341</t>
+          <t>74182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111824</t>
+          <t>113585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110612</t>
+          <t>112238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159143</t>
+          <t>160467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>632747</t>
+          <t>632797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>672799</t>
+          <t>671735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>590420</t>
+          <t>589553</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>638804</t>
+          <t>639127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1235351</t>
+          <t>1238519</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1297888</t>
+          <t>1300429</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59656</t>
+          <t>60213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95996</t>
+          <t>96542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86289</t>
+          <t>86056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124276</t>
+          <t>128437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157916</t>
+          <t>155786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212510</t>
+          <t>209699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20047</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42079</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50635</t>
+          <t>48025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79951</t>
+          <t>79528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75066</t>
+          <t>75642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112946</t>
+          <t>113102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>779143</t>
+          <t>782714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>822076</t>
+          <t>825872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>799928</t>
+          <t>796645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>853184</t>
+          <t>852951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1592918</t>
+          <t>1592587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1664211</t>
+          <t>1663034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69354</t>
+          <t>66468</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103648</t>
+          <t>101449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103018</t>
+          <t>104504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147012</t>
+          <t>148078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181077</t>
+          <t>182403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240077</t>
+          <t>238573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37257</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65229</t>
+          <t>63819</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73907</t>
+          <t>74694</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116088</t>
+          <t>116893</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118754</t>
+          <t>120407</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169872</t>
+          <t>170866</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2858151</t>
+          <t>2857004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2942999</t>
+          <t>2944841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2680789</t>
+          <t>2682849</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2784995</t>
+          <t>2784478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5571243</t>
+          <t>5573243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5711331</t>
+          <t>5708616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>303229</t>
+          <t>303815</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>376772</t>
+          <t>375847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>452231</t>
+          <t>452050</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>537256</t>
+          <t>542378</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>777451</t>
+          <t>777516</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>886340</t>
+          <t>884242</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>131610</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179169</t>
+          <t>179052</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>284283</t>
+          <t>279409</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>354970</t>
+          <t>355076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>426191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>515728</t>
+          <t>511439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2023</t>
+          <t>Población según limitación a subir varios pisos en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>507186</t>
+          <t>505387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>545139</t>
+          <t>544757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>552931</t>
+          <t>553609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>603991</t>
+          <t>604845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1070824</t>
+          <t>1072246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1134690</t>
+          <t>1131734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54636</t>
+          <t>55251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84132</t>
+          <t>85464</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72788</t>
+          <t>72530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108006</t>
+          <t>105930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135822</t>
+          <t>138041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182167</t>
+          <t>181421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54421</t>
+          <t>54298</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47387</t>
+          <t>47931</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72643</t>
+          <t>72235</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85054</t>
+          <t>84015</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118227</t>
+          <t>117420</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454855</t>
+          <t>406958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1057544</t>
+          <t>1057185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>720677</t>
+          <t>720844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>758449</t>
+          <t>760979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1066942</t>
+          <t>1052396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1782116</t>
+          <t>1785903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96042</t>
+          <t>96213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>719146</t>
+          <t>771124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133679</t>
+          <t>132187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>166269</t>
+          <t>167529</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>253327</t>
+          <t>249848</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1009995</t>
+          <t>1016665</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46775</t>
+          <t>47580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59733</t>
+          <t>59786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83945</t>
+          <t>84739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68496</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123984</t>
+          <t>123425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>555249</t>
+          <t>557422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>597284</t>
+          <t>597684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>721724</t>
+          <t>723686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>850318</t>
+          <t>855842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304069</t>
+          <t>1306129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1454272</t>
+          <t>1449019</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79020</t>
+          <t>77107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115819</t>
+          <t>113721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56491</t>
+          <t>51108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145287</t>
+          <t>144243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131939</t>
+          <t>130471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240517</t>
+          <t>239378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>43272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25578</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69766</t>
+          <t>68962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52665</t>
+          <t>50572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99736</t>
+          <t>101419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>765228</t>
+          <t>763704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>806418</t>
+          <t>803555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>818351</t>
+          <t>816537</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>894714</t>
+          <t>896131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1598898</t>
+          <t>1600590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1686967</t>
+          <t>1680479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78402</t>
+          <t>78937</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112223</t>
+          <t>113872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121820</t>
+          <t>123245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175695</t>
+          <t>177527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210273</t>
+          <t>214344</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274960</t>
+          <t>273891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36975</t>
+          <t>35280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59523</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76068</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111783</t>
+          <t>113142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120877</t>
+          <t>122754</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161453</t>
+          <t>162171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2130097</t>
+          <t>2136835</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2946401</t>
+          <t>2946868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2867523</t>
+          <t>2867724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3084092</t>
+          <t>3085463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4915696</t>
+          <t>5087714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5898884</t>
+          <t>5904243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>354394</t>
+          <t>353796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1217135</t>
+          <t>1210510</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>410088</t>
+          <t>405299</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>547076</t>
+          <t>547031</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>840011</t>
+          <t>836345</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1870835</t>
+          <t>1789488</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117959</t>
+          <t>118386</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176816</t>
+          <t>177154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>221814</t>
+          <t>226646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>309173</t>
+          <t>308848</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>367088</t>
+          <t>371618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>470483</t>
+          <t>472988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0802-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>580220</t>
+          <t>580479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>615895</t>
+          <t>615582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>505174</t>
+          <t>507115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>548264</t>
+          <t>548481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1098434</t>
+          <t>1097804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1153579</t>
+          <t>1153860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55372</t>
+          <t>55449</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87331</t>
+          <t>86505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108027</t>
+          <t>107478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147526</t>
+          <t>147122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172478</t>
+          <t>174220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223767</t>
+          <t>226175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16357</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35878</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>22971</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47238</t>
+          <t>45424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>44165</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75138</t>
+          <t>73066</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>814412</t>
+          <t>814893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>856524</t>
+          <t>858289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>717549</t>
+          <t>721210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>773070</t>
+          <t>774557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1552477</t>
+          <t>1548632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1617000</t>
+          <t>1616312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74536</t>
+          <t>73525</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111496</t>
+          <t>110534</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>147427</t>
+          <t>147824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>198080</t>
+          <t>195910</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231591</t>
+          <t>233760</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>291795</t>
+          <t>294110</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45895</t>
+          <t>46759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34718</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62787</t>
+          <t>62938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63136</t>
+          <t>63997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99918</t>
+          <t>100922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>553704</t>
+          <t>553898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>591978</t>
+          <t>591593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>489725</t>
+          <t>491860</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>533488</t>
+          <t>538034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1060376</t>
+          <t>1057879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1117025</t>
+          <t>1116506</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63138</t>
+          <t>62784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96643</t>
+          <t>96151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92805</t>
+          <t>92362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>130135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165267</t>
+          <t>164975</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215078</t>
+          <t>215009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37697</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45706</t>
+          <t>46018</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74435</t>
+          <t>75623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68673</t>
+          <t>69562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102738</t>
+          <t>105477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>789168</t>
+          <t>791181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>829758</t>
+          <t>831432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>774289</t>
+          <t>770643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>831200</t>
+          <t>827751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1579019</t>
+          <t>1576612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1644572</t>
+          <t>1645772</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78776</t>
+          <t>77725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112970</t>
+          <t>111640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138210</t>
+          <t>140307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187453</t>
+          <t>189480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230097</t>
+          <t>227044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288804</t>
+          <t>286061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26682</t>
+          <t>26859</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50548</t>
+          <t>48736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56032</t>
+          <t>58078</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90795</t>
+          <t>89474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91566</t>
+          <t>89882</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133728</t>
+          <t>129631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2780770</t>
+          <t>2781322</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2860304</t>
+          <t>2860798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2542685</t>
+          <t>2541509</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2641918</t>
+          <t>2635796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5353005</t>
+          <t>5346904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5475675</t>
+          <t>5479648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>301996</t>
+          <t>302022</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>371394</t>
+          <t>371413</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>532418</t>
+          <t>532922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>623494</t>
+          <t>622391</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>852849</t>
+          <t>846942</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>960674</t>
+          <t>962980</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101039</t>
+          <t>100447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143626</t>
+          <t>143189</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>184782</t>
+          <t>185594</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>243533</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>301104</t>
+          <t>297939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>371522</t>
+          <t>369738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>568256</t>
+          <t>567680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>608442</t>
+          <t>607260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>485124</t>
+          <t>485234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>532619</t>
+          <t>534336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1068120</t>
+          <t>1065851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1129553</t>
+          <t>1129836</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62123</t>
+          <t>61941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97389</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92068</t>
+          <t>94400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133333</t>
+          <t>133429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168197</t>
+          <t>166149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219574</t>
+          <t>219267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50831</t>
+          <t>51445</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57943</t>
+          <t>58801</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90340</t>
+          <t>92527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91308</t>
+          <t>91917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131309</t>
+          <t>130936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>826051</t>
+          <t>825702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>875306</t>
+          <t>875512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>739334</t>
+          <t>737172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>797659</t>
+          <t>800351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1581751</t>
+          <t>1582178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1656677</t>
+          <t>1658440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91483</t>
+          <t>92224</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133238</t>
+          <t>132563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130220</t>
+          <t>131649</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178453</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>233512</t>
+          <t>231450</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>295602</t>
+          <t>294601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41388</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71612</t>
+          <t>72906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89957</t>
+          <t>89359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130751</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138983</t>
+          <t>139666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189934</t>
+          <t>189887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>641570</t>
+          <t>638829</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>681602</t>
+          <t>681373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>571810</t>
+          <t>572401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>621896</t>
+          <t>620064</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1228361</t>
+          <t>1226831</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1290538</t>
+          <t>1290345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47658</t>
+          <t>48896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77833</t>
+          <t>81568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87009</t>
+          <t>87873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129158</t>
+          <t>125881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143334</t>
+          <t>144427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196334</t>
+          <t>193858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48406</t>
+          <t>48128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56831</t>
+          <t>58122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92039</t>
+          <t>91121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85322</t>
+          <t>86852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129024</t>
+          <t>130401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>763315</t>
+          <t>760886</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>810327</t>
+          <t>811212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>735415</t>
+          <t>735337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>795001</t>
+          <t>795105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1511620</t>
+          <t>1512730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1588644</t>
+          <t>1590328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89190</t>
+          <t>87991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130635</t>
+          <t>130286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169285</t>
+          <t>170824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>222051</t>
+          <t>223817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271494</t>
+          <t>270540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335730</t>
+          <t>336886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>36842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66222</t>
+          <t>65549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76065</t>
+          <t>72917</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111042</t>
+          <t>112468</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118773</t>
+          <t>119052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>165388</t>
+          <t>166470</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2847280</t>
+          <t>2843856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2935148</t>
+          <t>2932563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2588235</t>
+          <t>2586883</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2693905</t>
+          <t>2691041</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5464932</t>
+          <t>5453822</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5599342</t>
+          <t>5594276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,15%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>321248</t>
+          <t>325187</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>396264</t>
+          <t>398817</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>529916</t>
+          <t>524701</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>615914</t>
+          <t>612079</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>873010</t>
+          <t>868670</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>986556</t>
+          <t>986509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>147007</t>
+          <t>148336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202521</t>
+          <t>204958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>313393</t>
+          <t>310790</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>385717</t>
+          <t>383365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>482134</t>
+          <t>476902</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>568634</t>
+          <t>566675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>548967</t>
+          <t>551249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>586292</t>
+          <t>588127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>480763</t>
+          <t>479694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>524885</t>
+          <t>526031</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1042419</t>
+          <t>1040105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1101162</t>
+          <t>1101729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58363</t>
+          <t>56630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89841</t>
+          <t>90135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84667</t>
+          <t>84993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124399</t>
+          <t>121810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152508</t>
+          <t>151862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203328</t>
+          <t>203615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44614</t>
+          <t>44630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52983</t>
+          <t>52061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85189</t>
+          <t>84391</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80143</t>
+          <t>81939</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119707</t>
+          <t>120143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>854829</t>
+          <t>849653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>898118</t>
+          <t>897249</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>757862</t>
+          <t>760188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>817804</t>
+          <t>818273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1627291</t>
+          <t>1626624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1702006</t>
+          <t>1701989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86223</t>
+          <t>87272</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125783</t>
+          <t>125874</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>136527</t>
+          <t>134956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186916</t>
+          <t>187676</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>236342</t>
+          <t>235531</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>300096</t>
+          <t>297673</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>55236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74182</t>
+          <t>73058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113585</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112238</t>
+          <t>110829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160467</t>
+          <t>158591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>632797</t>
+          <t>632054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>671735</t>
+          <t>671954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>589553</t>
+          <t>591449</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>639127</t>
+          <t>638404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1238519</t>
+          <t>1240165</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1300429</t>
+          <t>1299459</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60213</t>
+          <t>59731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96542</t>
+          <t>93938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86056</t>
+          <t>86269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128437</t>
+          <t>127550</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155786</t>
+          <t>158878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209699</t>
+          <t>212893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>41984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>49223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79528</t>
+          <t>81135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75642</t>
+          <t>73929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113102</t>
+          <t>112783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>782714</t>
+          <t>781212</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>825872</t>
+          <t>823296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>796645</t>
+          <t>800255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>852951</t>
+          <t>853966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1592587</t>
+          <t>1592300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1663034</t>
+          <t>1665752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66468</t>
+          <t>68592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101449</t>
+          <t>101002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104504</t>
+          <t>103275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148078</t>
+          <t>145493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182403</t>
+          <t>183325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238573</t>
+          <t>237978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>37660</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63819</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74694</t>
+          <t>74873</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116893</t>
+          <t>113404</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120407</t>
+          <t>121962</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>170866</t>
+          <t>171193</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2857004</t>
+          <t>2861021</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2944841</t>
+          <t>2940475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2682849</t>
+          <t>2677664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2784478</t>
+          <t>2784706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5573243</t>
+          <t>5568949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5708616</t>
+          <t>5705241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>303815</t>
+          <t>304102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>375847</t>
+          <t>375660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>452050</t>
+          <t>451158</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>542378</t>
+          <t>535091</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>777516</t>
+          <t>774998</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>884242</t>
+          <t>887207</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131610</t>
+          <t>129325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179052</t>
+          <t>176594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>279409</t>
+          <t>281066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>355076</t>
+          <t>356239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>426191</t>
+          <t>425839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>511439</t>
+          <t>515283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>526619</t>
+          <t>572104</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>505387</t>
+          <t>552068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>544757</t>
+          <t>591071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>572400</t>
+          <t>570591</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>553609</t>
+          <t>551892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>604845</t>
+          <t>587015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1099020</t>
+          <t>1142694</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1072246</t>
+          <t>1115551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1131734</t>
+          <t>1166015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -8377,17 +8377,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68479</t>
+          <t>74449</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55251</t>
+          <t>60111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85464</t>
+          <t>91553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>98335</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72530</t>
+          <t>86044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105930</t>
+          <t>112354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>160553</t>
+          <t>172783</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138041</t>
+          <t>152924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181421</t>
+          <t>193509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40343</t>
+          <t>44157</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29913</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54298</t>
+          <t>56904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60856</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47931</t>
+          <t>54966</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72235</t>
+          <t>77670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>101199</t>
+          <t>109412</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84015</t>
+          <t>93677</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117420</t>
+          <t>128179</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>833886</t>
+          <t>923072</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406958</t>
+          <t>901390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1057185</t>
+          <t>942789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>739745</t>
+          <t>831124</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>720844</t>
+          <t>809202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>760979</t>
+          <t>851582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1573632</t>
+          <t>1754195</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1052396</t>
+          <t>1724147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1785903</t>
+          <t>1782446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>326150</t>
+          <t>90803</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96213</t>
+          <t>73472</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>771124</t>
+          <t>111414</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>147854</t>
+          <t>163143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132187</t>
+          <t>145825</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167529</t>
+          <t>183262</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>474005</t>
+          <t>253946</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>249848</t>
+          <t>228820</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1016665</t>
+          <t>280902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>25815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47580</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70507</t>
+          <t>76571</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59786</t>
+          <t>64351</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84739</t>
+          <t>90688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>103335</t>
+          <t>111613</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68878</t>
+          <t>96620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123425</t>
+          <t>128089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>578066</t>
+          <t>663474</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>557422</t>
+          <t>641770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>597684</t>
+          <t>684416</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>777490</t>
+          <t>634183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>723686</t>
+          <t>612135</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>855842</t>
+          <t>652821</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1355556</t>
+          <t>1297656</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306129</t>
+          <t>1268636</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1449019</t>
+          <t>1328776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94591</t>
+          <t>104280</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77107</t>
+          <t>84601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113721</t>
+          <t>122763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>106116</t>
+          <t>121962</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51108</t>
+          <t>105992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144243</t>
+          <t>140223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>200708</t>
+          <t>226242</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130471</t>
+          <t>200510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239378</t>
+          <t>250706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>47434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49759</t>
+          <t>56114</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24192</t>
+          <t>44733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68962</t>
+          <t>68625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>81036</t>
+          <t>90559</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>75109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101419</t>
+          <t>109566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>703933</t>
+          <t>802199</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>703933</t>
+          <t>802199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>703933</t>
+          <t>802199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1637299</t>
+          <t>1614457</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1637299</t>
+          <t>1614457</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1637299</t>
+          <t>1614457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>785839</t>
+          <t>844169</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>763704</t>
+          <t>821902</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>803555</t>
+          <t>864985</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>847124</t>
+          <t>850009</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>816537</t>
+          <t>825069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>896131</t>
+          <t>873189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1632963</t>
+          <t>1694178</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1600590</t>
+          <t>1664633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1680479</t>
+          <t>1727247</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94400</t>
+          <t>97678</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78937</t>
+          <t>81010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113872</t>
+          <t>116358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>151597</t>
+          <t>160506</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123245</t>
+          <t>141885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177527</t>
+          <t>179795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>245997</t>
+          <t>258184</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214344</t>
+          <t>233156</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273891</t>
+          <t>284860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>48215</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>36696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59426</t>
+          <t>60490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>95638</t>
+          <t>107950</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75916</t>
+          <t>93032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113142</t>
+          <t>124668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142230</t>
+          <t>156164</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122754</t>
+          <t>137632</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162171</t>
+          <t>178565</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094359</t>
+          <t>1118465</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094359</t>
+          <t>1118465</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094359</t>
+          <t>1118465</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2021190</t>
+          <t>2108527</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2021190</t>
+          <t>2108527</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2021190</t>
+          <t>2108527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2724411</t>
+          <t>3002818</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2136835</t>
+          <t>2958846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2946868</t>
+          <t>3038767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2936759</t>
+          <t>2885907</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2867724</t>
+          <t>2844887</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3085463</t>
+          <t>2925015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5661170</t>
+          <t>5888725</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5087714</t>
+          <t>5826941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5904243</t>
+          <t>5943712</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>583621</t>
+          <t>367211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>353796</t>
+          <t>336582</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1210510</t>
+          <t>405917</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>497642</t>
+          <t>543945</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>405299</t>
+          <t>514005</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>547031</t>
+          <t>578659</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1081262</t>
+          <t>911156</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>836345</t>
+          <t>865238</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1789488</t>
+          <t>959301</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>151039</t>
+          <t>161859</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118386</t>
+          <t>139707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>177154</t>
+          <t>186528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>276760</t>
+          <t>305890</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>226646</t>
+          <t>280808</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>308848</t>
+          <t>330548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>427799</t>
+          <t>467749</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>371618</t>
+          <t>435067</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>472988</t>
+          <t>504693</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3459070</t>
+          <t>3531888</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3459070</t>
+          <t>3531888</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3459070</t>
+          <t>3531888</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3711161</t>
+          <t>3735742</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3711161</t>
+          <t>3735742</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3711161</t>
+          <t>3735742</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7170231</t>
+          <t>7267629</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7170231</t>
+          <t>7267629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7170231</t>
+          <t>7267629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
